--- a/DataTables/Datas/#VSWeapon.xlsx
+++ b/DataTables/Datas/#VSWeapon.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,21 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>entityId</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hitEffectId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>knockback</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>desc</t>
         </is>
       </c>
@@ -476,6 +491,21 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
@@ -507,6 +537,21 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>弹体表现实体id(#Entity)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>命中特效实体id(#Entity)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>击退力度(首帧位移,单位)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
@@ -531,7 +576,16 @@
           <t>Nearest</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>500001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>701001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>自动索敌最近敌人，发射穿透弹</t>
         </is>
